--- a/Level1_Horizontal_Activation.xlsx
+++ b/Level1_Horizontal_Activation.xlsx
@@ -466,7 +466,7 @@
     <row r="2" ht="30" customHeight="1" s="12">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Choose 1 exercise from EACH section. 1 set, before the session. Ungraded, non-gating — doses stay the same throughout the program.</t>
+          <t>Pick 1 exercise from EACH section. 1 set, before the session. Ungraded and doesn't count toward clearing a phase — doses stay the same throughout the program.</t>
         </is>
       </c>
       <c r="G2" s="3" t="n"/>
@@ -554,7 +554,7 @@
     <row r="5" ht="15" customHeight="1" s="12">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>LAT LENGTH  ·  CHOOSE 1</t>
+          <t>LAT LENGTH  ·  PICK 1</t>
         </is>
       </c>
       <c r="G5" s="3" t="n"/>
@@ -655,7 +655,7 @@
     <row r="8" ht="15" customHeight="1" s="12">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>SHOULDER CAPSULE LENGTH  ·  CHOOSE 1</t>
+          <t>SHOULDER CAPSULE LENGTH  ·  PICK 1</t>
         </is>
       </c>
       <c r="G8" s="3" t="n"/>
@@ -719,7 +719,7 @@
     <row r="10" ht="15" customHeight="1" s="12">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>WRIST  ·  CHOOSE 1</t>
+          <t>WRIST  ·  PICK 1</t>
         </is>
       </c>
       <c r="G10" s="3" t="n"/>
@@ -820,7 +820,7 @@
     <row r="13" ht="15" customHeight="1" s="12">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>ELBOW  ·  CHOOSE 1</t>
+          <t>ELBOW  ·  PICK 1</t>
         </is>
       </c>
       <c r="G13" s="3" t="n"/>
@@ -958,7 +958,7 @@
     <row r="17" ht="15" customHeight="1" s="12">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>SERRATUS  ·  CHOOSE 1</t>
+          <t>SERRATUS  ·  PICK 1</t>
         </is>
       </c>
       <c r="G17" s="3" t="n"/>
@@ -1059,7 +1059,7 @@
     <row r="20" ht="15" customHeight="1" s="12">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>PEC LENGTH  ·  CHOOSE 1</t>
+          <t>PEC LENGTH  ·  PICK 1</t>
         </is>
       </c>
       <c r="G20" s="3" t="n"/>
@@ -1234,7 +1234,7 @@
     <row r="25" ht="15" customHeight="1" s="12">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>NECK / JAW  ·  CHOOSE 1  ·  NECK WORK IS OPTIONAL</t>
+          <t>NECK / JAW  ·  PICK 1  ·  NECK WORK IS OPTIONAL</t>
         </is>
       </c>
       <c r="G25" s="3" t="n"/>
